--- a/data/valuebets_database_2025-10-06.xlsx
+++ b/data/valuebets_database_2025-10-06.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,10 +505,8 @@
           <t>08/10 17:45</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>550.00</t>
-        </is>
+      <c r="F2" t="n">
+        <v>550</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -521,7 +519,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45936.06939084505</v>
+        <v>45936.06939084491</v>
       </c>
     </row>
     <row r="3">
@@ -550,10 +548,8 @@
           <t>08/10 18:15</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>350.00</t>
-        </is>
+      <c r="F3" t="n">
+        <v>350</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -566,7 +562,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45936.06939084505</v>
+        <v>45936.06939084491</v>
       </c>
     </row>
     <row r="4">
@@ -595,10 +591,8 @@
           <t>09/10 02:00</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F4" t="n">
+        <v>200</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -611,7 +605,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45936.06939084505</v>
+        <v>45936.06939084491</v>
       </c>
     </row>
     <row r="5">
@@ -640,10 +634,8 @@
           <t>08/10 17:00</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F5" t="n">
+        <v>175</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -656,7 +648,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45936.06939084505</v>
+        <v>45936.06939084491</v>
       </c>
     </row>
     <row r="6">
@@ -685,10 +677,8 @@
           <t>07/10 17:30</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F6" t="n">
+        <v>175</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -701,7 +691,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45936.06939084505</v>
+        <v>45936.06939084491</v>
       </c>
     </row>
     <row r="7">
@@ -730,10 +720,8 @@
           <t>07/10 17:00</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F7" t="n">
+        <v>175</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -746,7 +734,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45936.06939084505</v>
+        <v>45936.06939084491</v>
       </c>
     </row>
     <row r="8">
@@ -775,10 +763,8 @@
           <t>09/10 02:00</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F8" t="n">
+        <v>175</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -791,7 +777,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45936.06939084505</v>
+        <v>45936.06939084491</v>
       </c>
     </row>
     <row r="9">
@@ -820,10 +806,8 @@
           <t>08/10 15:30</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F9" t="n">
+        <v>175</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -836,7 +820,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45936.06939084505</v>
+        <v>45936.06939084491</v>
       </c>
     </row>
     <row r="10">
@@ -865,10 +849,8 @@
           <t>08/10 15:30</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F10" t="n">
+        <v>175</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -881,7 +863,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45936.06939084505</v>
+        <v>45936.06939084491</v>
       </c>
     </row>
     <row r="11">
@@ -910,10 +892,8 @@
           <t>08/10 23:00</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F11" t="n">
+        <v>175</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,7 +906,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45936.06939084505</v>
+        <v>45936.06939084491</v>
       </c>
     </row>
     <row r="12">
@@ -955,10 +935,8 @@
           <t>08/10 17:45</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F12" t="n">
+        <v>150</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -971,7 +949,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45936.06939084505</v>
+        <v>45936.06939084491</v>
       </c>
     </row>
     <row r="13">
@@ -1000,10 +978,8 @@
           <t>08/10 00:00</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F13" t="n">
+        <v>175</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1016,7 +992,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45936.06939084505</v>
+        <v>45936.06939084491</v>
       </c>
     </row>
     <row r="14">
@@ -1045,10 +1021,8 @@
           <t>10/10 17:45</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F14" t="n">
+        <v>150</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1061,7 +1035,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45936.06939084505</v>
+        <v>45936.06939084491</v>
       </c>
     </row>
     <row r="15">
@@ -1090,10 +1064,8 @@
           <t>10/10 16:00</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F15" t="n">
+        <v>150</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1106,7 +1078,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45936.06939084505</v>
+        <v>45936.06939084491</v>
       </c>
     </row>
     <row r="16">
@@ -1135,10 +1107,8 @@
           <t>10/10 16:00</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F16" t="n">
+        <v>140</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1151,7 +1121,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45936.06939084505</v>
+        <v>45936.06939084491</v>
       </c>
     </row>
     <row r="17">
@@ -1180,10 +1150,8 @@
           <t>08/10 18:20</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F17" t="n">
+        <v>150</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1196,7 +1164,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45936.06939084505</v>
+        <v>45936.06939084491</v>
       </c>
     </row>
     <row r="18">
@@ -1225,10 +1193,8 @@
           <t>08/10 23:30</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F18" t="n">
+        <v>150</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1241,7 +1207,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45936.06939084505</v>
+        <v>45936.06939084491</v>
       </c>
     </row>
     <row r="19">
@@ -1270,10 +1236,8 @@
           <t>08/10 02:30</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F19" t="n">
+        <v>150</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1286,7 +1250,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45936.06939084505</v>
+        <v>45936.06939084491</v>
       </c>
     </row>
     <row r="20">
@@ -1315,10 +1279,8 @@
           <t>09/10 18:00</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F20" t="n">
+        <v>125</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1331,7 +1293,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45936.06939084505</v>
+        <v>45936.06939084491</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1322,8 @@
           <t>10/10 16:00</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F21" t="n">
+        <v>125</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1376,7 +1336,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45936.06939084505</v>
+        <v>45936.06939084491</v>
       </c>
     </row>
     <row r="22">
@@ -1405,10 +1365,8 @@
           <t>10/10 15:30</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F22" t="n">
+        <v>125</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1421,7 +1379,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45936.06939084505</v>
+        <v>45936.06939084491</v>
       </c>
     </row>
     <row r="23">
@@ -1450,10 +1408,8 @@
           <t>07/10 21:00</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F23" t="n">
+        <v>140</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1466,7 +1422,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45936.06939084505</v>
+        <v>45936.06939084491</v>
       </c>
     </row>
     <row r="24">
@@ -1495,10 +1451,8 @@
           <t>07/10 17:30</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F24" t="n">
+        <v>125</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1511,7 +1465,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45936.06939084505</v>
+        <v>45936.06939084491</v>
       </c>
     </row>
     <row r="25">
@@ -1540,23 +1494,201 @@
           <t>08/10 16:00</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" t="n">
+        <v>125</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>+83,1%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>45936.06939084491</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Pas de buts | Brynäs IF </t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Brynäs IF – Storhamar IL DragonsEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>07/10 17:00</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>+176%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>45936.12749524944</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Fribourg G</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Fribourg Gotteron – Kloten FlyersSuisse - Suisse NLA stq pr cu 385076e7</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>09/10 18:00</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+120%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>45936.12749524944</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Rögle BK –</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Rögle BK – Växjö Lakers HCSuède - Suède SHL</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>09/10 17:00</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>125.00</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>1,46%</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>+83,1%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="n">
-        <v>45936.06939084505</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+78,7%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45936.12749524944</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | Orebro HK </t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Orebro HK – Timra IKSHL</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>09/10 17:00</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+78,1%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45936.12749524944</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-06.xlsx
+++ b/data/valuebets_database_2025-10-06.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1537,10 +1537,8 @@
           <t>07/10 17:00</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F26" t="n">
+        <v>200</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1553,7 +1551,7 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>45936.12749524944</v>
+        <v>45936.12749525463</v>
       </c>
     </row>
     <row r="27">
@@ -1582,10 +1580,8 @@
           <t>09/10 18:00</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F27" t="n">
+        <v>140</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1598,7 +1594,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45936.12749524944</v>
+        <v>45936.12749525463</v>
       </c>
     </row>
     <row r="28">
@@ -1627,10 +1623,8 @@
           <t>09/10 17:00</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F28" t="n">
+        <v>125</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1643,7 +1637,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45936.12749524944</v>
+        <v>45936.12749525463</v>
       </c>
     </row>
     <row r="29">
@@ -1672,10 +1666,8 @@
           <t>09/10 17:00</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F29" t="n">
+        <v>110</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1688,7 +1680,142 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45936.12749524944</v>
+        <v>45936.12749525463</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Kärpät Oul</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Kärpät Oulu – JYP JyväskyläFinlande - Finlande Liiga</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>08/10 15:30</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+138%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45936.18394225602</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Pas de buts | Olomouc – </t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Olomouc – Kometa BrnoRép. Tchèque - Rép. Tchèque Extraliga</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>10/10 16:00</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+96,5%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45936.18394225602</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Zilina – K</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Zilina – KosiceSlovaquie - Slovaquie Extraliga</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>10/10 15:30</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+94,0%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45936.18394225602</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-06.xlsx
+++ b/data/valuebets_database_2025-10-06.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1709,10 +1709,8 @@
           <t>08/10 15:30</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F30" t="n">
+        <v>175</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1725,7 +1723,7 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>45936.18394225602</v>
+        <v>45936.18394225695</v>
       </c>
     </row>
     <row r="31">
@@ -1754,10 +1752,8 @@
           <t>10/10 16:00</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F31" t="n">
+        <v>125</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1770,7 +1766,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45936.18394225602</v>
+        <v>45936.18394225695</v>
       </c>
     </row>
     <row r="32">
@@ -1799,10 +1795,8 @@
           <t>10/10 15:30</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F32" t="n">
+        <v>125</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1815,7 +1809,97 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45936.18394225602</v>
+        <v>45936.18394225695</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Tappara Ta</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Tappara Tampere – KooKooFinlande - Finlande Liiga</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>08/10 15:30</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+173%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>45936.22284950126</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Rapperswil</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Rapperswil Jona Lakers – ZSC LionsSuisse - Suisse NLA</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>10/10 17:45</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+141%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45936.22284950126</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-06.xlsx
+++ b/data/valuebets_database_2025-10-06.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1838,10 +1838,8 @@
           <t>08/10 15:30</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F33" t="n">
+        <v>200</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1854,7 +1852,7 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45936.22284950126</v>
+        <v>45936.22284950232</v>
       </c>
     </row>
     <row r="34">
@@ -1883,23 +1881,246 @@
           <t>10/10 17:45</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" t="n">
+        <v>150</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+141%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45936.22284950232</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Slovan Bra</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Slovan Bratislava – Mhk 32 Liptovsky MikulasExtraliga</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>10/10 16:30</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+155%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45936.27282885649</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Zug – Genè</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Zug – Genève-ServetteSuisse - Suisse NLA</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>10/10 17:45</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
         <is>
           <t>150.00</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>+141%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="n">
-        <v>45936.22284950126</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+131%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45936.27282885649</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | HC Presov </t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>HC Presov – NitraExtraliga</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>10/10 16:00</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+131%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45936.27282885649</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Lausanne –</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Lausanne – EHC Biel-Bienne385076e7 Suisse - Suisse NLA</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>10/10 17:45</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+99,1%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45936.27282885649</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Dukla Tren</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Dukla Trencin – Dukla MichalovceExtraliga</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>10/10 16:00</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+97,4%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45936.27282885649</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-06.xlsx
+++ b/data/valuebets_database_2025-10-06.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1924,10 +1924,8 @@
           <t>10/10 16:30</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F35" t="n">
+        <v>200</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1940,7 +1938,7 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45936.27282885649</v>
+        <v>45936.27282885417</v>
       </c>
     </row>
     <row r="36">
@@ -1969,10 +1967,8 @@
           <t>10/10 17:45</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F36" t="n">
+        <v>150</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1985,7 +1981,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45936.27282885649</v>
+        <v>45936.27282885417</v>
       </c>
     </row>
     <row r="37">
@@ -2014,10 +2010,8 @@
           <t>10/10 16:00</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F37" t="n">
+        <v>150</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2030,7 +2024,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45936.27282885649</v>
+        <v>45936.27282885417</v>
       </c>
     </row>
     <row r="38">
@@ -2059,10 +2053,8 @@
           <t>10/10 17:45</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F38" t="n">
+        <v>125</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2075,7 +2067,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>45936.27282885649</v>
+        <v>45936.27282885417</v>
       </c>
     </row>
     <row r="39">
@@ -2104,10 +2096,8 @@
           <t>10/10 16:00</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F39" t="n">
+        <v>140</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2120,7 +2110,52 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>45936.27282885649</v>
+        <v>45936.27282885417</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Banska Bys</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Banska Bystrica – Spisska Nova VesExtraliga</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>10/10 15:30</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+98,4%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45936.30709537388</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-06.xlsx
+++ b/data/valuebets_database_2025-10-06.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2139,23 +2139,156 @@
           <t>10/10 15:30</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F40" t="n">
+        <v>125</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+98,4%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45936.30709537037</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | HK Poprad </t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>HK Poprad – HKM AS ZvolenExtraliga</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>10/10 16:00</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1,60%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+140%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45936.35365640719</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Lausanne –</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Lausanne – EHC BielNational League A</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>10/10 17:45</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
         <is>
           <t>125.00</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>+98,4%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="n">
-        <v>45936.30709537388</v>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1,60%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>+100%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>45936.35365640719</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | HC Kometa </t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>HC Kometa Brno – Ilves TampereLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>08/10 16:00</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>+95,9%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>45936.35365640719</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-06.xlsx
+++ b/data/valuebets_database_2025-10-06.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2182,10 +2182,8 @@
           <t>10/10 16:00</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F41" t="n">
+        <v>150</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2198,7 +2196,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45936.35365640719</v>
+        <v>45936.35365641204</v>
       </c>
     </row>
     <row r="42">
@@ -2227,10 +2225,8 @@
           <t>10/10 17:45</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F42" t="n">
+        <v>125</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2243,7 +2239,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45936.35365640719</v>
+        <v>45936.35365641204</v>
       </c>
     </row>
     <row r="43">
@@ -2272,10 +2268,8 @@
           <t>08/10 16:00</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F43" t="n">
+        <v>125</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2288,7 +2282,52 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45936.35365640719</v>
+        <v>45936.35365641204</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Slovan Bra</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Slovan Bratislava – Liptovsky MikulasSlovaquie - Slovaquie Extraliga</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>10/10 16:30</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+189%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>45936.3925474451</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-06.xlsx
+++ b/data/valuebets_database_2025-10-06.xlsx
@@ -2311,10 +2311,8 @@
           <t>10/10 16:30</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F44" t="n">
+        <v>200</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2327,7 +2325,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45936.3925474451</v>
+        <v>45936.39254744213</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-06.xlsx
+++ b/data/valuebets_database_2025-10-06.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2328,6 +2328,51 @@
         <v>45936.39254744213</v>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Grenoble –</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Grenoble – LausanneLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>08/10 18:15</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>+196%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>45936.56308766502</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-10-06.xlsx
+++ b/data/valuebets_database_2025-10-06.xlsx
@@ -2354,10 +2354,8 @@
           <t>08/10 18:15</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F45" t="n">
+        <v>200</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2370,7 +2368,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45936.56308766502</v>
+        <v>45936.56308766203</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-06.xlsx
+++ b/data/valuebets_database_2025-10-06.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2371,6 +2371,411 @@
         <v>45936.56308766203</v>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Odense Bul</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Odense Bulldogs – SalzbourgEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>08/10 17:00</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>+155%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45936.64030509655</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Pas de buts | Bolzano – </t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Bolzano – IngolstadtEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>08/10 17:45</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>+124%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>45936.64030509655</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Malmö Redh</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Malmö Redhawks – Frölunda HCSuède - Suède SHL</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>09/10 17:00</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>125.00</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>+103%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>45936.64030509655</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Pas de buts | Örebro HK </t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Örebro HK – Timrå IKSuède - Suède SHL</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>09/10 17:00</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>110.00</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>+85,0%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>45936.64030509655</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Betsson(FR)Hockey | Pas de buts | Fischtown </t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Fischtown Pinguins – Lulea HockeyInternational - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>07/10 17:30</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>101.00</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>+80,0%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>45936.64030509655</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Betsson(FR)Hockey | Pas de buts | ZSC Lions </t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>ZSC Lions – Sparta PragueInternational - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>07/10 17:45</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>+79,1%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>45936.64030509655</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Hockey | Pas de buts | Neftekhimi</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Neftekhimik Nijnekamsk – Amur KhabarovskRussie - KHL</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>07/10 16:00</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>1,77%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>+77,3%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>45936.64030509655</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Ambri Piot</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ambri Piotta – AjoieSuisse - Suisse NLA</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>10/10 17:45</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>99.00</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>+73,9%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>45936.64030509655</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Hockey | Pas de buts | Torpedo Ni</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Betsson(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Torpedo Nijni Novgorod – Metallurg MagnitogorskRussie - KHL</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>07/10 16:00</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>101.00</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>+72,5%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>45936.64030509655</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-10-06.xlsx
+++ b/data/valuebets_database_2025-10-06.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2397,10 +2397,8 @@
           <t>08/10 17:00</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F46" t="n">
+        <v>175</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2413,7 +2411,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45936.64030509655</v>
+        <v>45936.64030509259</v>
       </c>
     </row>
     <row r="47">
@@ -2442,10 +2440,8 @@
           <t>08/10 17:45</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F47" t="n">
+        <v>150</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2458,7 +2454,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>45936.64030509655</v>
+        <v>45936.64030509259</v>
       </c>
     </row>
     <row r="48">
@@ -2487,10 +2483,8 @@
           <t>09/10 17:00</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F48" t="n">
+        <v>125</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2503,7 +2497,7 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>45936.64030509655</v>
+        <v>45936.64030509259</v>
       </c>
     </row>
     <row r="49">
@@ -2532,10 +2526,8 @@
           <t>09/10 17:00</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>110.00</t>
-        </is>
+      <c r="F49" t="n">
+        <v>110</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2548,7 +2540,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>45936.64030509655</v>
+        <v>45936.64030509259</v>
       </c>
     </row>
     <row r="50">
@@ -2577,10 +2569,8 @@
           <t>07/10 17:30</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>101.00</t>
-        </is>
+      <c r="F50" t="n">
+        <v>101</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2593,7 +2583,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>45936.64030509655</v>
+        <v>45936.64030509259</v>
       </c>
     </row>
     <row r="51">
@@ -2622,10 +2612,8 @@
           <t>07/10 17:45</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F51" t="n">
+        <v>100</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2638,7 +2626,7 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>45936.64030509655</v>
+        <v>45936.64030509259</v>
       </c>
     </row>
     <row r="52">
@@ -2667,10 +2655,8 @@
           <t>07/10 16:00</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F52" t="n">
+        <v>100</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2683,7 +2669,7 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>45936.64030509655</v>
+        <v>45936.64030509259</v>
       </c>
     </row>
     <row r="53">
@@ -2712,10 +2698,8 @@
           <t>10/10 17:45</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>99.00</t>
-        </is>
+      <c r="F53" t="n">
+        <v>99</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2728,7 +2712,7 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>45936.64030509655</v>
+        <v>45936.64030509259</v>
       </c>
     </row>
     <row r="54">
@@ -2757,10 +2741,8 @@
           <t>07/10 16:00</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>101.00</t>
-        </is>
+      <c r="F54" t="n">
+        <v>101</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2773,7 +2755,367 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45936.64030509655</v>
+        <v>45936.64030509259</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | EC VSV – I</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>EC VSV – Innsbruck Die HaieAutriche - Autriche ICE</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>11/10 13:00</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>+202%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>45936.68554224356</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Nurnberg I</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Nurnberg Ice Tigers – MunichAllemagne - Allemagne DEL</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>09/10 17:30</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>+181%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>45936.68554224356</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | Nashville </t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Nashville Predators – Columbus Blue JacketsNHL</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>10/10 00:00</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>+174%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>45936.68554224356</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Olimpija L</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Olimpija Ljubljana – Black Wings LinzAutriche - Autriche ICE</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>10/10 17:15</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>+151%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>45936.68554224356</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Cologne Ha</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Cologne Haie – ERC IngolstadtDEL</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>10/10 17:30</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>+141%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>45936.68554224356</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | San Jose S</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>San Jose Sharks – Vegas Golden KnightsNHL</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>10/10 02:00</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>+140%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>45936.68554224356</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Lowen Fran</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Lowen Frankfurt – BerlinDEL</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>10/10 17:30</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>+135%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>45936.68554224356</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | Straubing </t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Straubing – Wild WingsDEL</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>10/10 17:30</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>+129%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>45936.68554224356</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-06.xlsx
+++ b/data/valuebets_database_2025-10-06.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I62"/>
+  <dimension ref="A1:I67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2784,10 +2784,8 @@
           <t>11/10 13:00</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F55" t="n">
+        <v>200</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2800,7 +2798,7 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>45936.68554224356</v>
+        <v>45936.68554224537</v>
       </c>
     </row>
     <row r="56">
@@ -2829,10 +2827,8 @@
           <t>09/10 17:30</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F56" t="n">
+        <v>200</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2845,7 +2841,7 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>45936.68554224356</v>
+        <v>45936.68554224537</v>
       </c>
     </row>
     <row r="57">
@@ -2874,10 +2870,8 @@
           <t>10/10 00:00</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F57" t="n">
+        <v>200</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2890,7 +2884,7 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>45936.68554224356</v>
+        <v>45936.68554224537</v>
       </c>
     </row>
     <row r="58">
@@ -2919,10 +2913,8 @@
           <t>10/10 17:15</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F58" t="n">
+        <v>150</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2935,7 +2927,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>45936.68554224356</v>
+        <v>45936.68554224537</v>
       </c>
     </row>
     <row r="59">
@@ -2964,10 +2956,8 @@
           <t>10/10 17:30</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F59" t="n">
+        <v>175</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2980,7 +2970,7 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>45936.68554224356</v>
+        <v>45936.68554224537</v>
       </c>
     </row>
     <row r="60">
@@ -3009,10 +2999,8 @@
           <t>10/10 02:00</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F60" t="n">
+        <v>175</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3025,7 +3013,7 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>45936.68554224356</v>
+        <v>45936.68554224537</v>
       </c>
     </row>
     <row r="61">
@@ -3054,10 +3042,8 @@
           <t>10/10 17:30</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F61" t="n">
+        <v>175</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3070,7 +3056,7 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>45936.68554224356</v>
+        <v>45936.68554224537</v>
       </c>
     </row>
     <row r="62">
@@ -3099,23 +3085,246 @@
           <t>10/10 17:30</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F62" t="n">
+        <v>175</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>+129%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>45936.68554224537</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | EC Villach</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>EC Villacher SV – HC Twk Innsbruck Die HaieICE</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>11/10 13:00</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>+201%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>45936.72168566765</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Buffalo Sa</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Buffalo Sabres – NY RangersNHL</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>09/10 23:00</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>1,33%</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>+166%</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>45936.72168566765</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | Tampa Bay </t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Tampa Bay Lightning – Ottawa SenatorsNHL</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>09/10 23:00</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>1,33%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>+166%</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>45936.72168566765</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Augsburger</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Augsburger Panther – Wolfsburg GrizzlyAllemagne - Allemagne DEL</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>10/10 17:30</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
         <is>
           <t>175.00</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>+164%</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>45936.72168566765</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Colorado A</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Colorado Avalanche – Utah Hockey ClubNHL</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>10/10 01:00</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
         <is>
           <t>1,31%</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>+129%</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="n">
-        <v>45936.68554224356</v>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>+162%</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>45936.72168566765</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-06.xlsx
+++ b/data/valuebets_database_2025-10-06.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:I68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3128,10 +3128,8 @@
           <t>11/10 13:00</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F63" t="n">
+        <v>200</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3144,7 +3142,7 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>45936.72168566765</v>
+        <v>45936.7216856713</v>
       </c>
     </row>
     <row r="64">
@@ -3173,10 +3171,8 @@
           <t>09/10 23:00</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F64" t="n">
+        <v>200</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3189,7 +3185,7 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>45936.72168566765</v>
+        <v>45936.7216856713</v>
       </c>
     </row>
     <row r="65">
@@ -3218,10 +3214,8 @@
           <t>09/10 23:00</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F65" t="n">
+        <v>200</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3234,7 +3228,7 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>45936.72168566765</v>
+        <v>45936.7216856713</v>
       </c>
     </row>
     <row r="66">
@@ -3263,10 +3257,8 @@
           <t>10/10 17:30</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F66" t="n">
+        <v>175</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3279,7 +3271,7 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>45936.72168566765</v>
+        <v>45936.7216856713</v>
       </c>
     </row>
     <row r="67">
@@ -3308,23 +3300,66 @@
           <t>10/10 01:00</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F67" t="n">
+        <v>200</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>+162%</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>45936.7216856713</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Detroit Re</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Detroit Red Wings – Montreal CanadiensNHL</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>09/10 23:00</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
         <is>
           <t>200.00</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>+162%</t>
-        </is>
-      </c>
-      <c r="I67" s="2" t="n">
-        <v>45936.72168566765</v>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>+171%</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>45936.77195157434</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-06.xlsx
+++ b/data/valuebets_database_2025-10-06.xlsx
@@ -3343,10 +3343,8 @@
           <t>09/10 23:00</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F68" t="n">
+        <v>200</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3359,7 +3357,7 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>45936.77195157434</v>
+        <v>45936.77195157408</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-06.xlsx
+++ b/data/valuebets_database_2025-10-06.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I68"/>
+  <dimension ref="A1:I69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3360,6 +3360,51 @@
         <v>45936.77195157408</v>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | Nuremberg </t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Nuremberg Ice Tigers – EHC MunichDEL</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>09/10 17:30</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>+169%</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>45936.84953638486</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-10-06.xlsx
+++ b/data/valuebets_database_2025-10-06.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I69"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3386,10 +3386,8 @@
           <t>09/10 17:30</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F69" t="n">
+        <v>175</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3402,7 +3400,52 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>45936.84953638486</v>
+        <v>45936.84953638889</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Hockey | Pas de buts | SC Bern – </t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>SC Bern – Belfast GiantsLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>08/10 17:45</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>+168%</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>45936.8880131286</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-06.xlsx
+++ b/data/valuebets_database_2025-10-06.xlsx
@@ -3429,10 +3429,8 @@
           <t>08/10 17:45</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F70" t="n">
+        <v>200</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3445,7 +3443,7 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>45936.8880131286</v>
+        <v>45936.888013125</v>
       </c>
     </row>
   </sheetData>
